--- a/output/Muster_Honorarrechnung-Lehrkräfte_February.xlsx
+++ b/output/Muster_Honorarrechnung-Lehrkräfte_February.xlsx
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C36" s="26" t="inlineStr">
         <is>
-          <t>Unterricht ASA 9 Vertretung</t>
+          <t>Vorbereitung + Unterricht ASA 9 Vertretung start 15:30</t>
         </is>
       </c>
       <c r="D36" s="16" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C38" s="26" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8</t>
+          <t>Unterricht ASA 8 Vertretung</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
